--- a/data/trans_orig/P36B03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B03-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27468</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>28166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62280</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56449</t>
+          <t>57728</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88952</t>
+          <t>88248</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43674</t>
+          <t>42977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72712</t>
+          <t>72375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66327</t>
+          <t>64254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101215</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117283</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165328</t>
+          <t>161689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924099</t>
+          <t>924438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>959881</t>
+          <t>961696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1131793</t>
+          <t>1132463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1178703</t>
+          <t>1178911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2069064</t>
+          <t>2068960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2127960</t>
+          <t>2127415</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21685</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44465</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20837</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55117</t>
+          <t>54625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59189</t>
+          <t>58402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46094</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75192</t>
+          <t>76462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85557</t>
+          <t>83135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125756</t>
+          <t>124641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78192</t>
+          <t>78679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116437</t>
+          <t>117950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90733</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131545</t>
+          <t>132369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181876</t>
+          <t>180780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237538</t>
+          <t>233585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1502278</t>
+          <t>1504305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1552881</t>
+          <t>1553915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1340840</t>
+          <t>1340324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1395139</t>
+          <t>1396199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2860289</t>
+          <t>2861410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2932709</t>
+          <t>2936013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>18817</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30064</t>
+          <t>31822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49735</t>
+          <t>50755</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29748</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56134</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28968</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>53461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64948</t>
+          <t>65395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100948</t>
+          <t>98838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>468399</t>
+          <t>467942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>500066</t>
+          <t>498849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>394721</t>
+          <t>395527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>424203</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>869749</t>
+          <t>870989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>915818</t>
+          <t>915085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>34641</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>28431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52545</t>
+          <t>53713</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46052</t>
+          <t>46159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80200</t>
+          <t>76675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30077</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>50095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82453</t>
+          <t>81770</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65182</t>
+          <t>65811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102236</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>106622</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151291</t>
+          <t>151459</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>182455</t>
+          <t>179061</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239843</t>
+          <t>239966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>169587</t>
+          <t>166662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>223119</t>
+          <t>221540</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>203358</t>
+          <t>200184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>264378</t>
+          <t>261295</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>387489</t>
+          <t>389352</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>464847</t>
+          <t>470048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2919877</t>
+          <t>2921567</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2990339</t>
+          <t>2990581</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2890076</t>
+          <t>2896156</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2974787</t>
+          <t>2975112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5836901</t>
+          <t>5842747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5942405</t>
+          <t>5945869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33471</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34205</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48762</t>
+          <t>52944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44019</t>
+          <t>45286</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75664</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53198</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88097</t>
+          <t>88779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79861</t>
+          <t>80103</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120347</t>
+          <t>119436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>895225</t>
+          <t>896296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>926427</t>
+          <t>927089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1182954</t>
+          <t>1180095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1229558</t>
+          <t>1226338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2086726</t>
+          <t>2090364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2144285</t>
+          <t>2146151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,77 +4394,77 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17298</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10183</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27808</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>30514</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>21061</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>43799</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17298</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10613</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27589</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>30514</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>20505</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>44129</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48539</t>
+          <t>48458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>50453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82460</t>
+          <t>82031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79540</t>
+          <t>76295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118123</t>
+          <t>118416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56663</t>
+          <t>56700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89847</t>
+          <t>90254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66243</t>
+          <t>67723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104803</t>
+          <t>106370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134221</t>
+          <t>134084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183984</t>
+          <t>181949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1817308</t>
+          <t>1818519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1861707</t>
+          <t>1863687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1553897</t>
+          <t>1550354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1605819</t>
+          <t>1604348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3385794</t>
+          <t>3388399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3454459</t>
+          <t>3454006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18247</t>
+          <t>19270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44470</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43715</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46503</t>
+          <t>47113</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48768</t>
+          <t>45941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81664</t>
+          <t>80097</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>415521</t>
+          <t>416674</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>446576</t>
+          <t>446069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>377428</t>
+          <t>377475</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>407711</t>
+          <t>408841</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>803301</t>
+          <t>804321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>846535</t>
+          <t>848582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46080</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40595</t>
+          <t>40521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71990</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48394</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32840</t>
+          <t>32939</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>62499</t>
+          <t>62393</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>51486</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84364</t>
+          <t>84992</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98991</t>
+          <t>100051</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>145931</t>
+          <t>145089</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>159918</t>
+          <t>159550</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>214608</t>
+          <t>218611</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>108171</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153539</t>
+          <t>156515</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,47 +6092,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>187457</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>159686</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>216246</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>4,49%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>187457</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>162120</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>217091</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>278798</t>
+          <t>281330</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>351537</t>
+          <t>356552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3156677</t>
+          <t>3156448</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3219578</t>
+          <t>3216921</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3134000</t>
+          <t>3137122</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3218710</t>
+          <t>3217579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6319408</t>
+          <t>6321481</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6419075</t>
+          <t>6418666</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23506</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>48794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48565</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53735</t>
+          <t>54488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88194</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681311</t>
+          <t>681510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>710505</t>
+          <t>711777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908606</t>
+          <t>907932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>941575</t>
+          <t>941458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1601825</t>
+          <t>1601051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1644068</t>
+          <t>1642680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>31259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>25972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47742</t>
+          <t>47412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33736</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63329</t>
+          <t>61410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38842</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68445</t>
+          <t>67676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77678</t>
+          <t>78074</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118045</t>
+          <t>118564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>101430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144002</t>
+          <t>145992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61819</t>
+          <t>61745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95457</t>
+          <t>96567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174942</t>
+          <t>170745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227783</t>
+          <t>227145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1847106</t>
+          <t>1845159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1900639</t>
+          <t>1901770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1791331</t>
+          <t>1787370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1840676</t>
+          <t>1840615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3652625</t>
+          <t>3655001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3725162</t>
+          <t>3729162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>30606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43126</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35272</t>
+          <t>36079</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67485</t>
+          <t>66932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>495138</t>
+          <t>496801</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>521435</t>
+          <t>520886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>487666</t>
+          <t>485345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>514811</t>
+          <t>513950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>992188</t>
+          <t>991848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1029042</t>
+          <t>1028552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>35015</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46313</t>
+          <t>46599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42655</t>
+          <t>43003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75334</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>32186</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>19550</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>43363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>37904</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66090</t>
+          <t>67156</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>52727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88250</t>
+          <t>88955</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>64750</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101735</t>
+          <t>99698</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125832</t>
+          <t>125542</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174066</t>
+          <t>175140</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>149799</t>
+          <t>150508</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203398</t>
+          <t>200126</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119021</t>
+          <t>119377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>167329</t>
+          <t>166859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>278271</t>
+          <t>283667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>351486</t>
+          <t>352343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3047242</t>
+          <t>3048961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3116513</t>
+          <t>3116571</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3210048</t>
+          <t>3208593</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3280016</t>
+          <t>3274905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6282123</t>
+          <t>6279027</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6374689</t>
+          <t>6375034</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42670</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47127</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>19482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>23321</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>33173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21247</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>45502</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>59496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>28717</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>52147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70491</t>
+          <t>78219</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59572</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83007</t>
+          <t>92288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>101282</t>
+          <t>116003</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87593</t>
+          <t>99131</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117312</t>
+          <t>133869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>456986</t>
+          <t>508503</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>442986</t>
+          <t>491635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>468569</t>
+          <t>521670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>629734</t>
+          <t>688653</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608331</t>
+          <t>670860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>644985</t>
+          <t>704967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1086720</t>
+          <t>1197156</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1061432</t>
+          <t>1172441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1107125</t>
+          <t>1219106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>22867</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29996</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60407</t>
+          <t>64101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>24165</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>364144</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>92880</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60509</t>
+          <t>74745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116937</t>
+          <t>118066</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87789</t>
+          <t>95885</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>79079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109963</t>
+          <t>113442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>176747</t>
+          <t>188766</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>139460</t>
+          <t>164442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>209448</t>
+          <t>219490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>230988</t>
+          <t>259664</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164571</t>
+          <t>226659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277530</t>
+          <t>294911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>234505</t>
+          <t>267112</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177181</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278872</t>
+          <t>296495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>465493</t>
+          <t>526776</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>372487</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>529559</t>
+          <t>578088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1942660</t>
+          <t>1848662</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1884397</t>
+          <t>1803834</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2065700</t>
+          <t>1887074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1802570</t>
+          <t>1758577</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1632461</t>
+          <t>1726003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1904815</t>
+          <t>1792214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3745230</t>
+          <t>3607240</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3554503</t>
+          <t>3550105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3877068</t>
+          <t>3658651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2236284</t>
+          <t>2169753</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2236284</t>
+          <t>2169753</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2236284</t>
+          <t>2169753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4526611</t>
+          <t>4400320</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4526611</t>
+          <t>4400320</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4526611</t>
+          <t>4400320</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35435</t>
+          <t>38127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18924</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>29885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45549</t>
+          <t>48854</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47914</t>
+          <t>52618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>70424</t>
+          <t>76228</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56909</t>
+          <t>60721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90037</t>
+          <t>93425</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92233</t>
+          <t>100202</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>81126</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113563</t>
+          <t>122963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>81112</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67500</t>
+          <t>76251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96640</t>
+          <t>107324</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>173345</t>
+          <t>190602</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149971</t>
+          <t>166609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200562</t>
+          <t>215060</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>502633</t>
+          <t>557784</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>478704</t>
+          <t>528364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>524577</t>
+          <t>578915</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>519482</t>
+          <t>576606</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>499092</t>
+          <t>556366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>537540</t>
+          <t>594453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1022115</t>
+          <t>1134390</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>991737</t>
+          <t>1105997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1048469</t>
+          <t>1164312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>60222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>49087</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36308</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70097</t>
+          <t>62462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>89221</t>
+          <t>90874</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68041</t>
+          <t>74137</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117718</t>
+          <t>112295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32806</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>111043</t>
+          <t>49139</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>37732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>390190</t>
+          <t>65395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>131982</t>
+          <t>73814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59600</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>369112</t>
+          <t>92691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>134555</t>
+          <t>141621</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>102547</t>
+          <t>118743</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>164756</t>
+          <t>171890</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>168875</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>124052</t>
+          <t>147667</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179543</t>
+          <t>191160</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>288756</t>
+          <t>310496</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>248743</t>
+          <t>279389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>332901</t>
+          <t>347783</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>354012</t>
+          <t>397649</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>278685</t>
+          <t>354893</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>404402</t>
+          <t>439868</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>386107</t>
+          <t>435732</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>321690</t>
+          <t>404439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430499</t>
+          <t>471930</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>740119</t>
+          <t>833381</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>643959</t>
+          <t>783447</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>813210</t>
+          <t>886965</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2902280</t>
+          <t>2914951</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2839537</t>
+          <t>2864564</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3020509</t>
+          <t>2964627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2951786</t>
+          <t>3023835</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2759316</t>
+          <t>2978035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3054182</t>
+          <t>3061730</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5854066</t>
+          <t>5938786</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5648950</t>
+          <t>5875408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6005123</t>
+          <t>6003412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652255</t>
+          <t>3726668</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3652255</t>
+          <t>3726668</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652255</t>
+          <t>3726668</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7104144</t>
+          <t>7247351</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7104144</t>
+          <t>7247351</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7104144</t>
+          <t>7247351</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
